--- a/hira_material_automation/output/monthly/202601_202608__acl_interference_screw_absorbable__040012__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202608__acl_interference_screw_absorbable__040012__normalized.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-04T22:17:02</t>
+          <t>2026-08-14T21:29:03</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>083825e19245a861238c16dfce19fb3e5f80ceb0a5047643800bed7581ec155a</t>
+          <t>7c704c89d8f5ecbf9db6cc6fb39ae4147a851e448a96b8a16c3d3a7e41eba603</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202608__acl_interference_screw_absorbable__040012__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202608__acl_interference_screw_absorbable__040012__normalized.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-14T21:29:03</t>
+          <t>2026-08-24T21:34:11</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7c704c89d8f5ecbf9db6cc6fb39ae4147a851e448a96b8a16c3d3a7e41eba603</t>
+          <t>41f8ae7f2d7889f6751a52886f1ca465b637786af50dc7a7c759bc59358f5b49</t>
         </is>
       </c>
     </row>
